--- a/www/download/COUNTRY.IRL.zdW16.xlsx
+++ b/www/download/COUNTRY.IRL.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>Irlanda</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1.08271957831817</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1.11664801106905</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1.05750220729866</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.883988518955073</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>0.803987735984668</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.80378717688062</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>0.796334689423854</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0.729656768802188</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.679884186748212</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.716968497971946</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0.75431519360931</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>0.718393578907381</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.778332869326693</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>0.753108745496249</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.752731589313597</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.712</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1.763</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1.792</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.888</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1.979</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2.071</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2.163</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2.147</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.971</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1.885</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>1.849</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.839</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1.882</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1.914</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1.398</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1.447</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1.475</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1.509</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1.559</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.744</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.805</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1.779</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.637</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.574</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>1.554</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.544</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1.565</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1.593</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3226.327</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3310.464</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3323.682</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>3359.551</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>3455.104</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>3642.632</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>3805.262</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>3942.466</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>3875.257</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>3502.182</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>3330.611</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>3276.519</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>3268.551</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>3364.626</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>3429.051</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2614.474</t>
+          <t>3618428353.32083</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2694.332</t>
+          <t>4121848865.18492</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2714.471</t>
+          <t>4083289462.27368</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2754.193</t>
+          <t>4477215098.10321</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2825.752</t>
+          <t>4679076156.12117</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3011.362</t>
+          <t>5124164403.17322</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3178.716</t>
+          <t>5576343495.57051</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3263.874</t>
+          <t>5342790007.37113</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3188.589</t>
+          <t>4918753920.02572</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2891.487</t>
+          <t>4357488578.78025</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2766.921</t>
+          <t>3217336175.05767</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2735.885</t>
+          <t>3671831973.16641</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2731.447</t>
+          <t>3578084370.48385</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2780.543</t>
+          <t>3983264213.7407</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2838.109</t>
+          <t>4008284760.40187</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1048884396.19534</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1287750482.22365</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1367035279.05852</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1363797884.97533</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1611157692.61184</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1785662199.9489</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1897756801.10736</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1906580242.90069</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1868318348.15367</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1403838448.87262</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>869631405.132415</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1202162660.54825</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1124813596.73393</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1174644670.80733</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1093345958.51722</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1245167.33615578</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1300677.22207554</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1178135.91400159</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>949871.838146777</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>819706.403409702</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>836733.651503914</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>780724.273959988</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>667606.892255644</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>599304.089466499</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>738336.828262872</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>672432.087341549</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>627630.794770632</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>711956.417032952</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>698227.636848398</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>701717.075607621</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>15595.0129606973</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15810.8392668149</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>15819.7902795098</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>17315.4580765308</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>19707.5462383362</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>22179.7290555287</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>24478.4647867592</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>28062.6752885328</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>29541.6500548574</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>23617.7510384029</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>24324.7654502247</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>25354.331220415</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>24282.4811405441</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>25318.9242947058</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>26043.6696410938</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>32823.9930959416</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>36843.1901193284</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>36766.9994694645</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>43889.8782772105</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>50548.2535234676</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>59789.699437168</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>68755.8114110977</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>73897.7300231051</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>74200.7416840815</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>60073.9240422694</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>49004.9929216263</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>59631.3581596236</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>56761.6225304444</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>62822.876643545</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>63438.1879323581</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.49262360035441</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.09227799732407</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.985662726911818</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.01950232533894</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.753864325607498</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.686411909310829</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.674985961396734</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.711899623503027</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.706662573405148</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.05970067447723</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2.18171697074198</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.27580267611396</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.42835524742159</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.3671354147369</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.59580142761857</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271957831817</t>
+          <t>750.371575879114</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11664801106905</t>
+          <t>889.865100041907</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05750220729866</t>
+          <t>926.834997158223</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.883988518955073</t>
+          <t>903.80588155693</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803987735984668</t>
+          <t>1033.66803488326</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.80378717688062</t>
+          <t>1082.4228794191</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796334689423854</t>
+          <t>1088.41918174993</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729656768802188</t>
+          <t>1056.48200088698</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679884186748212</t>
+          <t>1049.92966903273</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716968497971946</t>
+          <t>857.384462010334</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.75431519360931</t>
+          <t>552.420503571556</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.718393578907381</t>
+          <t>773.428204144715</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.778332869326693</t>
+          <t>728.676114077074</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.753108745496249</t>
+          <t>750.384677816601</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.752731589313597</t>
+          <t>686.374139803521</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>3050311257.91574</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>3927395948.4341</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>4907386033.86858</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>5365670399.08237</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>5712074238.85576</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>5179567500.4214</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>4858537072.99264</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>4963338374.41528</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>4576312671.94976</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>5260531344.43469</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>4554706534.61078</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>5316282232.87151</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>4903834941.16491</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>5528863486.40554</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>5442677528.41113</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>4223210863.59945</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>4989337480.72962</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>6080979449.88381</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>6283655767.62611</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>6715517247.58276</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>6260263223.59496</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>5621386199.38924</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>5586488946.67615</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>5413212005.38761</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>6781058516.23412</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>6286471688.75743</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>6894246180.70475</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>5991497867.29248</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>5856252666.46497</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>6425233677.13827</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-1172899605.68371</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>-1061941532.29552</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1173593416.01523</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>-917985368.543736</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>-1003443008.727</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>-1080695723.17356</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-762849126.396592</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>-623150572.26087</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-836899333.437859</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>-1520527171.79943</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.532</t>
+          <t>-1731765154.14665</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>-1577963947.83324</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>-1087662926.12757</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>-327389180.059429</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>-982556148.727141</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>1870.39389907141</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>1861.84516940427</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>1840.3817078545</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>1825.23807945923</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>1812.91349090256</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>1825.41083476289</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>1823.08684954605</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>1808.59113955615</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.623</t>
+          <t>1791.87567084581</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>1765.95535468898</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>1757.64569119945</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1760.16997677456</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1769.48446528983</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>1776.26214553562</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.509</t>
+          <t>1781.69097198245</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>1884.81207192698</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>1877.36128447374</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1855.03327855729</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>1840.31550422636</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>1829.67553915406</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>1841.07069219458</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>1837.27912971321</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1822.71810740517</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>1805.13170537436</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>1776.81948807188</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>1767.22138947977</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>1771.64683694506</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>1777.82600638023</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>1787.71678375247</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>1791.27271107644</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>81845.867387007</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>92774.3080690981</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>106927.11160932</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>129679.45707317</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>152525.514333605</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>164217.431011896</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>178752.334501396</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>212877.852038687</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>226867.074435184</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>216714.768235318</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>222048.262499347</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>240906.236470089</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>231379.768491338</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>242962.72234118</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>262751.14906643</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1487424439.64809</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1672322915.30451</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1574467894.10991</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1760293082.90974</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1835389308.21409</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2032185953.02489</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2078072173.33532</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1993931662.5556</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1774703527.31834</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1881447855.63059</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1645484300.62664</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1978180732.71819</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1901812784.71709</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2104910473.98876</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2166696279.77852</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>65803.0597558543</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>73016.3275917728</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>81335.8409587086</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>100485.51975363</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>120049.933415598</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>135530.45590191</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>153548.003585728</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>181982.846583246</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>192894.779294372</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>176406.092819597</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>179339.460640752</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>189864.395743022</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>186150.976148024</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>190713.866824103</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>211026.349289831</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3226.327</t>
+          <t>2343803308.38187</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3310.464</t>
+          <t>2787548218.31321</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3323.682</t>
+          <t>2816453660.18195</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3359.551</t>
+          <t>3184496812.46075</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3455.104</t>
+          <t>3552192941.92492</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3642.632</t>
+          <t>4010884630.2098</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3805.262</t>
+          <t>4384321897.31845</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3942.466</t>
+          <t>4274612277.9634</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3875.257</t>
+          <t>3775617249.59046</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3502.182</t>
+          <t>3709626521.62734</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>3330.611</t>
+          <t>2958272293.88554</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>3276.519</t>
+          <t>3626556754.62308</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>3268.551</t>
+          <t>3533819881.85918</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>3364.626</t>
+          <t>3816433089.73717</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>3429.051</t>
+          <t>3866615433.87513</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2614.474</t>
+          <t>16042.8076311527</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2694.332</t>
+          <t>19757.9804773253</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2714.471</t>
+          <t>25591.2706506116</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2754.193</t>
+          <t>29193.9373195405</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2825.752</t>
+          <t>32475.5809180069</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3011.362</t>
+          <t>28686.9751099867</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3178.716</t>
+          <t>25204.330915668</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>3263.874</t>
+          <t>30895.0054554412</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3188.589</t>
+          <t>33972.295140812</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2891.487</t>
+          <t>40308.675415721</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2766.921</t>
+          <t>42708.8018585956</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2735.885</t>
+          <t>51041.840727067</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2731.447</t>
+          <t>45228.7923433139</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2780.543</t>
+          <t>52248.8555170773</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2838.109</t>
+          <t>51724.7997765994</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4025.151</t>
+          <t>-856378868.733775</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4599.33</t>
+          <t>-1115225303.00871</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4583.766</t>
+          <t>-1241985766.07204</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>5076.083</t>
+          <t>-1424203729.55101</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>5290.409</t>
+          <t>-1716803633.71082</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>5820.437</t>
+          <t>-1978698677.18491</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>6348.538</t>
+          <t>-2306249723.98313</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>6049.528</t>
+          <t>-2280680615.4078</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>5591.839</t>
+          <t>-2000913722.27212</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>5205.993</t>
+          <t>-1828178665.99675</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>3838.202</t>
+          <t>-1312787993.2589</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>4488.818</t>
+          <t>-1648376021.90489</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>4346.297</t>
+          <t>-1632007097.14209</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>4811.275</t>
+          <t>-1711522615.74841</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>4008.285</t>
+          <t>-1699919154.09661</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>44457.76308</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>50857.72072</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>61181.2656</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>74335.45056</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>85924.00957</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>90850.90014</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>99510.19236</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>112968.53335</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>111499.73012</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>98238.5536</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>88970.3784</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>101425.8528</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>90583.92464</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>93938.50515</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>96995.51205</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1719.152</t>
+          <t>0.203685044173383</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1768.845</t>
+          <t>0.200752909117004</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1756.923</t>
+          <t>0.205590372563792</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1766.353</t>
+          <t>0.193569933958503</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1824.259</t>
+          <t>0.175494340587914</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1900.872</t>
+          <t>0.163776278013791</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1985.291</t>
+          <t>0.158967623156696</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2028.925</t>
+          <t>0.161180489681809</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1958.311</t>
+          <t>0.152939459246518</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1713.124</t>
+          <t>0.152054256936105</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1596.999</t>
+          <t>0.173660892690595</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1561.206</t>
+          <t>0.195887535019324</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1530.696</t>
+          <t>0.18927973177188</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1605.338</t>
+          <t>0.18962635252134</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1645.546</t>
+          <t>0.182859963426392</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>38546.7989693078</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>41765.0523258937</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>47350.3526900227</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>61661.7119600428</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>73709.5339091297</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>82221.287599275</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>91349.2953698279</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>109248.036998324</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>120191.716906966</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>103493.602167895</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>90713.9390466425</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>95244.9552013011</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>87291.753113915</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>90732.3837710149</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>93918.4403530152</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1166.896</t>
+          <t>46254.6152544787</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1430.469</t>
+          <t>49924.600495315</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1526.727</t>
+          <t>56418.2248736946</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1531.221</t>
+          <t>73151.7273415185</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1797.951</t>
+          <t>87552.07745356</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2003.033</t>
+          <t>96880.4071191097</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2136.371</t>
+          <t>106849.930737734</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2132.746</t>
+          <t>129001.584877783</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2098.786</t>
+          <t>142177.466275306</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1612.838</t>
+          <t>123802.469803946</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>998.967</t>
+          <t>108305.262476958</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1384.326</t>
+          <t>112507.840575246</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1296.773</t>
+          <t>103032.765155381</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1349.449</t>
+          <t>107538.412342932</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1093.346</t>
+          <t>111211.18801935</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>124.05</t>
+          <t>210488.082094703</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>235338.784501443</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>279697.093862628</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>79.87</t>
+          <t>377725.448382955</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>57.17</t>
+          <t>474648.271376918</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>50.34</t>
+          <t>539236.923988292</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>610118.312572804</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>53.04</t>
+          <t>685810.913922469</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>51.93</t>
+          <t>680194.349283315</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>79.28</t>
+          <t>579066.535980496</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>176.98</t>
+          <t>532316.500900772</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>97.63</t>
+          <t>564394.791114537</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>110.63</t>
+          <t>542576.250201426</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>106.05</t>
+          <t>581300.426743562</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>159.58</t>
+          <t>636832.894770653</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>82046.4117676014</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>81840.2197625747</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>77692.617698139</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>73221.0280950988</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.939</t>
+          <t>73000.2489453547</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.961</t>
+          <t>75006.081736282</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>76001.7187026762</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>79798.1353745675</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>84948.0042769329</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>80776.4938173541</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>75454.9156798155</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.813</t>
+          <t>74208.3306771148</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.916</t>
+          <t>71012.3198301178</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>68598.1605136564</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>72326.6299945821</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>69504.1314413578</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>69231.4360006256</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>65776.1450104518</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>62147.869551548</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>61700.8013957132</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>63838.5075817523</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>65616.1181669466</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>68550.8430019719</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>72360.9571949182</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>66191.4555410424</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>63199.3131007721</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>63204.4884816368</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>60555.8182359677</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>58854.7865704425</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>62133.1365659341</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>42873.2742994303</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>47244.9456167244</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>57503.0297322277</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>73116.2900979346</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>83298.0853964854</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>88314.2163784082</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>96989.0579940727</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>110539.338935153</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>104028.555961927</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>88049.5318450786</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>92442.5587403618</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>110557.904409173</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>102698.687103918</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>110229.87964248</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>116451.239846485</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2614474000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2694332000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2714471000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2754193000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2825752000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3011362000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>3178716000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>3263874000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3188589000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2891487000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2766921000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2735885000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2731447000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2780543000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2838109000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3226327064.12101</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3310463794.58961</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3323681675.52388</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>3359551162.43036</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3455104397.87236</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>3642632007.33466</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>3805262296.71422</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>3942466357.59309</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>3875256745.09768</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3502182283.7692</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>3330611463.89694</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>3276519093.18294</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>3268550890.99011</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>3364626004.36484</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>3429051263.54074</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1719152112.37264</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1768844925.70998</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1756922889.43378</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1766353277.19902</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1824259064.78933</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1900872209.89968</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1985291498.91123</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2028925395.47284</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1958310708.40268</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1713123989.26867</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1596999472.23671</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1561206165.79226</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1530695606.85917</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1605338221.70772</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1645545806.55181</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1711750</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1763360</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1791710</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1825530</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1888370</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1978540</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2071140</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2162960</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2146800</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1971040</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1884660</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1849420</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1838510</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1882080</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1914310</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1397820</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1447130</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1474950</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1508950</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1558680</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1649690</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1743590</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1804650</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1779470</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1637350</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1574220</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1554330</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1543640</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1565390</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1592930</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3226327064.12101</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3310463794.58961</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3323681675.52388</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3359551162.43036</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3455104397.87236</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3642632007.33466</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3805262296.71422</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3942466357.59309</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3875256745.09768</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3502182283.7692</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>3330611463.89694</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>3276519093.18294</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>3268550890.99011</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>3364626004.36484</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>3429051263.54074</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2614474000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2694332000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2714471000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2754193000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2825752000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3011362000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3178716000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3263874000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3188589000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2891487000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2766921000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2735885000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2731447000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2780543000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2838109000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>204392.12584</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>222582.03504</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>256656.54864</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>334341.31808</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>395322.11754</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>434691.89907</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>492880.38092</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>581314.8433</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>623311.8028</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>523515.8632</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>465506.82828</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>480215.2224</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>450359.91616</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>481233.58194</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>509477.093</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>89127.95416</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>97169.55496</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>113921.25456</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>146268.00608</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>170850.16256</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>185194.73544</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>203839.00084</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>239540.9238</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>246206.0368</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>211851.9876</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>200747.83446</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>223065.7728</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>205731.42656</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>217768.29138</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>227662.388</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>367861.473879245</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>380631.329005969</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>394484.324188302</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>439045.460230835</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>517379.889335708</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>635503.049066623</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>678971.503984988</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>573622.947930526</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>435251.369355611</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>481106.970011059</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>370858.06135019</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>317085.529623986</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>333689.78965574</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>347761.578192541</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>407509.571213566</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
